--- a/telecom_input_27E.xlsx
+++ b/telecom_input_27E.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O46"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -950,7 +950,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2. 유선 순신규</t>
+          <t>2. 유선</t>
         </is>
       </c>
       <c r="B16" s="5" t="n"/>
@@ -1080,64 +1080,64 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>3. 대당 단가 (단가 변동 있을 시)</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="5" t="n"/>
-      <c r="O22" s="6" t="n"/>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  유선 정책수수료 (총액)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>백만원 (26E: 11,369)</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="11">
+        <f>SUM(C21:N21)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  대당 상품매출 (PU)</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>원/건</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n"/>
-      <c r="I23" s="11" t="n"/>
-      <c r="J23" s="11" t="n"/>
-      <c r="K23" s="11" t="n"/>
-      <c r="L23" s="11" t="n"/>
-      <c r="M23" s="11" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="11">
-        <f>SUM(C23:N23)</f>
-        <v/>
-      </c>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3. 무선 대당 단가 (단가 변동 있을 시)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  대당 수수료매출 (CU)</t>
+          <t xml:space="preserve">  대당 상품매출 (PU)</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>원/건</t>
+          <t>원/건 (26E: 708,268)</t>
         </is>
       </c>
       <c r="C24" s="11" t="n"/>
@@ -1160,12 +1160,12 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  대당 정책수수료</t>
+          <t xml:space="preserve">  대당 수수료매출 (CU)</t>
         </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>원/건</t>
+          <t>원/건 (26E: 760,673)</t>
         </is>
       </c>
       <c r="C25" s="11" t="n"/>
@@ -1188,12 +1188,12 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  대당 관리수수료</t>
+          <t xml:space="preserve">  무선 대당 정책수수료</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>원/매장</t>
+          <t>원/건 (26E: 247,338)</t>
         </is>
       </c>
       <c r="C26" s="11" t="n"/>
@@ -1213,228 +1213,228 @@
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  대당 관리수수료</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>원/매장</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11">
+        <f>SUM(C27:N27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>4. 매장수</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="5" t="n"/>
-      <c r="I28" s="5" t="n"/>
-      <c r="J28" s="5" t="n"/>
-      <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="5" t="n"/>
-      <c r="N28" s="5" t="n"/>
-      <c r="O28" s="6" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  소매 매장수 (26E 참고)</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n">
+      <c r="C30" s="8" t="n">
         <v>251</v>
       </c>
-      <c r="D29" s="8" t="n">
+      <c r="D30" s="8" t="n">
         <v>251</v>
       </c>
-      <c r="E29" s="8" t="n">
+      <c r="E30" s="8" t="n">
         <v>251</v>
       </c>
-      <c r="F29" s="8" t="n">
+      <c r="F30" s="8" t="n">
         <v>252</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G30" s="8" t="n">
         <v>254</v>
       </c>
-      <c r="H29" s="8" t="n">
+      <c r="H30" s="8" t="n">
         <v>256</v>
       </c>
-      <c r="I29" s="8" t="n">
+      <c r="I30" s="8" t="n">
         <v>258</v>
       </c>
-      <c r="J29" s="8" t="n">
+      <c r="J30" s="8" t="n">
         <v>260</v>
       </c>
-      <c r="K29" s="8" t="n">
+      <c r="K30" s="8" t="n">
         <v>262</v>
       </c>
-      <c r="L29" s="8" t="n">
+      <c r="L30" s="8" t="n">
         <v>264</v>
       </c>
-      <c r="M29" s="8" t="n">
+      <c r="M30" s="8" t="n">
         <v>266</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N30" s="8" t="n">
         <v>270</v>
       </c>
-      <c r="O29" s="8" t="n">
+      <c r="O30" s="8" t="n">
         <v>3095</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  소매 매장수</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
-      <c r="I30" s="11" t="n"/>
-      <c r="J30" s="11" t="n"/>
-      <c r="K30" s="11" t="n"/>
-      <c r="L30" s="11" t="n"/>
-      <c r="M30" s="11" t="n"/>
-      <c r="N30" s="11" t="n"/>
-      <c r="O30" s="11">
-        <f>SUM(C30:N30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11">
+        <f>SUM(C31:N31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  도매 매장수 (26E 참고)</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n">
+      <c r="C32" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="D31" s="8" t="n">
+      <c r="D32" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="E31" s="8" t="n">
+      <c r="E32" s="8" t="n">
         <v>41</v>
       </c>
-      <c r="F31" s="8" t="n">
+      <c r="F32" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="G31" s="8" t="n">
+      <c r="G32" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H32" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="I31" s="8" t="n">
+      <c r="I32" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J32" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="K31" s="8" t="n">
+      <c r="K32" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="L31" s="8" t="n">
+      <c r="L32" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M32" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N32" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="O31" s="8" t="n">
+      <c r="O32" s="8" t="n">
         <v>462</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  도매 매장수</t>
         </is>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>개</t>
         </is>
       </c>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="11" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="11" t="n"/>
-      <c r="K32" s="11" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="11">
-        <f>SUM(C32:N32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11">
+        <f>SUM(C33:N33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>5. 인력 (HC)</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="5" t="n"/>
-      <c r="O34" s="6" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  정규직 인원</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>명</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="11">
-        <f>SUM(C35:N35)</f>
-        <v/>
-      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  영업직 인원</t>
+          <t xml:space="preserve">  정규직 인원</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -1462,7 +1462,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  도급/계약직 인원</t>
+          <t xml:space="preserve">  영업직 인원</t>
         </is>
       </c>
       <c r="B37" s="10" t="inlineStr">
@@ -1490,12 +1490,12 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  임금인상률 (연간)</t>
+          <t xml:space="preserve">  도급/계약직 인원</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
         <is>
-          <t>% (예: 3.5)</t>
+          <t>명</t>
         </is>
       </c>
       <c r="C38" s="11" t="n"/>
@@ -1515,49 +1515,64 @@
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  임금인상률 (연간)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>% (예: 3.5)</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="11" t="n"/>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="11">
+        <f>SUM(C39:N39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>6. 비용 가정 (연간)</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n"/>
-      <c r="C40" s="5" t="n"/>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
-      <c r="H40" s="5" t="n"/>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-      <c r="K40" s="5" t="n"/>
-      <c r="L40" s="5" t="n"/>
-      <c r="M40" s="5" t="n"/>
-      <c r="N40" s="5" t="n"/>
-      <c r="O40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  통신 원가율 개선 목표</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>% (예: 0.5 = 0.5%p 개선)</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CAPEX 투자계획</t>
+          <t xml:space="preserve">  통신 원가율 개선 목표</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
         <is>
-          <t>백만원</t>
+          <t>% (예: 0.5 = 0.5%p 개선)</t>
         </is>
       </c>
       <c r="C42" s="13" t="n"/>
@@ -1565,12 +1580,12 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  감가상각 내용연수</t>
+          <t xml:space="preserve">  CAPEX 투자계획</t>
         </is>
       </c>
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>년</t>
+          <t>백만원</t>
         </is>
       </c>
       <c r="C43" s="13" t="n"/>
@@ -1578,12 +1593,12 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  임차료 증감률</t>
+          <t xml:space="preserve">  감가상각 내용연수</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>% (예: 2.5)</t>
+          <t>년</t>
         </is>
       </c>
       <c r="C44" s="13" t="n"/>
@@ -1591,12 +1606,12 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  마케팅비 증감률</t>
+          <t xml:space="preserve">  임차료 증감률</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>% (예: 2.0)</t>
+          <t>% (예: 2.5)</t>
         </is>
       </c>
       <c r="C45" s="13" t="n"/>
@@ -1604,26 +1619,39 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">  마케팅비 증감률</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>% (예: 2.0)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">  판촉비 증감률</t>
         </is>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B47" s="10" t="inlineStr">
         <is>
           <t>% (예: 3.0)</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A40:O40"/>
+    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="A35:O35"/>
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A2:O2"/>
-    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="A41:O41"/>
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A23:O23"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="A22:O22"/>
-    <mergeCell ref="A34:O34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
